--- a/stories/arbres/ATOM-FAM.VER.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Zoé est dans le salon. Un verre d'eau a glissé. L'eau est sur la table. Zoé a un nœud au ventre. Papa est près de la fenêtre. Maman est dans la cuisine. Zoé va vers papa. Elle va raconter. Elle dit : papa, le verre a glissé. Papa l'écoute. Maman arrive. Zoé raconte aussi à maman. Papa dit : merci d'avoir su raconter. On le dit à papa ou maman. Zoé aide à essuyer. Le nœud se desserre.</t>
+          <t>Zoé est dans le salon. Un verre d'eau a glissé. L'eau est sur la table. Zoé a un nœud au ventre. Papa est près de la fenêtre. Maman est dans la cuisine. Zoé va vers papa. Elle va raconter. Papa, le verre a glissé. Papa l'écoute. Maman arrive. Zoé raconte aussi à maman. Merci d'avoir su raconter. On le dit à papa ou maman. Zoé aide à essuyer. Le nœud se desserre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé est dans le salon. Un verre d'eau a glissé. L'eau est sur la table. Zoé a un nœud au ventre. Papa est près de la fenêtre. Maman est dans la cuisine. Zoé va vers papa. Elle va raconter.
+narrateur|Papa, le verre a glissé. Papa l'écoute. Maman arrive.
+narrateur|Zoé raconte aussi à maman.
+papa|Merci d'avoir su raconter. On le dit à papa ou maman.
+narrateur|Zoé aide à essuyer. Le nœud se desserre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le verre a glissé. Que fait Zoé ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a raconté. Papa et maman ont écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa pose un nouveau verre. Zoé sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Zoé aide à essuyer. Le nœud se desserre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Le verre a glissé. Que fait Zoé ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Zoé a raconté. Papa et maman ont écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Papa pose un nouveau verre. Zoé sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.VER.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zoé raconte le verre d'eau</t>
+          <t>Amir raconte le verre d'eau</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un verre glisse. L'eau est sur la table. Amir a un nœud au ventre. Il raconte à papa, puis à maman. Ils essuient ensemble.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Zoé est dans le salon. Un verre d'eau a glissé. L'eau est sur la table. Zoé a un nœud au ventre. Papa est près de la fenêtre. Maman est dans la cuisine. Zoé va vers papa. Elle va raconter. Papa, le verre a glissé. Papa l'écoute. Maman arrive. Zoé raconte aussi à maman. Merci d'avoir su raconter. On le dit à papa ou maman. Zoé aide à essuyer. Le nœud se desserre.</t>
+          <t>L'horloge du salon fait tic. Un rideau se lève un peu. Le vent entre, tout doux. Un coussin bleu a une petite boucle. La nappe est lisse sous la main. Un rayon de soleil touche la table. Le bois sent le chaud. Une mouche marche sur la vitre. Elle fait un petit point noir. Le coussin bleu est un peu rêche. Tu as entendu l'horloge, Amir ? Oui, papa. Elle fait tic. Le rideau danse un peu. Tu le vois ? Oui. Il va et vient. En ce moment, Amir touche le verre. Un verre d'eau a glissé. L'eau est sur la table. Elle fait une tache claire. Amir a un nœud au ventre. Papa est près de la fenêtre. Maman est dans la cuisine. Amir va vers papa. Il va raconter. Papa, le verre a glissé. L'eau est sur la table. Je t'écoute, Amir. Merci d'avoir su raconter. On le dit à papa ou maman. Tu as fait du bon travail. Tu veux le torchon ? Oui, papa. Maman arrive. Elle sent le savon de la cuisine. Maman, le verre a glissé. J'ai raconté à papa. Je t'écoute aussi. Merci Amir. On raconte à papa ou maman. Bravo. On essuie ensemble ? Oui. Amir aide à essuyer. Le torchon est épais et un peu rêche. La tache part. Le nœud se desserre. Tu veux un nouveau verre, plus loin ? Oui. Plus loin. On le pose au milieu, d'accord ? D'accord. Papa pose le verre, tout doucement. Il ne tremble plus. Le nœud au ventre, il est parti ? Oui, papa. Presque. Tu as su raconter. Ça aide.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,73 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Zoé est dans le salon. Un verre d'eau a glissé. L'eau est sur la table. Zoé a un nœud au ventre. Papa est près de la fenêtre. Maman est dans la cuisine. Zoé va vers papa. Elle va raconter.
-narrateur|Papa, le verre a glissé. Papa l'écoute. Maman arrive.
-narrateur|Zoé raconte aussi à maman.
-papa|Merci d'avoir su raconter. On le dit à papa ou maman.
-narrateur|Zoé aide à essuyer. Le nœud se desserre.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|L'horloge du salon fait tic.
+narrateur|Un rideau se lève un peu.
+narrateur|Le vent entre, tout doux.
+narrateur|Un coussin bleu a une petite boucle.
+narrateur|La nappe est lisse sous la main.
+narrateur|Un rayon de soleil touche la table.
+narrateur|Le bois sent le chaud.
+narrateur|Une mouche marche sur la vitre.
+narrateur|Elle fait un petit point noir.
+narrateur|Le coussin bleu est un peu rêche.
+papa|Tu as entendu l'horloge, Amir ?
+enfant-m|Oui, papa.
+enfant-m|Elle fait tic.
+papa|Le rideau danse un peu.
+papa|Tu le vois ?
+enfant-m|Oui.
+enfant-m|Il va et vient.
+narrateur|En ce moment, Amir touche le verre.
+narrateur|Un verre d'eau a glissé.
+narrateur|L'eau est sur la table.
+narrateur|Elle fait une tache claire.
+narrateur|Amir a un nœud au ventre.
+narrateur|Papa est près de la fenêtre.
+narrateur|Maman est dans la cuisine.
+narrateur|Amir va vers papa.
+narrateur|Il va raconter.
+enfant-m|Papa, le verre a glissé.
+enfant-m|L'eau est sur la table.
+papa|Je t'écoute, Amir.
+papa|Merci d'avoir su raconter.
+papa|On le dit à papa ou maman.
+papa|Tu as fait du bon travail.
+papa|Tu veux le torchon ?
+enfant-m|Oui, papa.
+narrateur|Maman arrive.
+narrateur|Elle sent le savon de la cuisine.
+enfant-m|Maman, le verre a glissé.
+enfant-m|J'ai raconté à papa.
+maman|Je t'écoute aussi.
+maman|Merci Amir.
+maman|On raconte à papa ou maman.
+maman|Bravo.
+maman|On essuie ensemble ?
+enfant-m|Oui.
+narrateur|Amir aide à essuyer.
+narrateur|Le torchon est épais et un peu rêche.
+narrateur|La tache part.
+narrateur|Le nœud se desserre.
+papa|Tu veux un nouveau verre, plus loin ?
+enfant-m|Oui.
+enfant-m|Plus loin.
+maman|On le pose au milieu, d'accord ?
+enfant-m|D'accord.
+narrateur|Papa pose le verre, tout doucement.
+narrateur|Il ne tremble plus.
+papa|Le nœud au ventre, il est parti ?
+enfant-m|Oui, papa.
+enfant-m|Presque.
+maman|Tu as su raconter.
+maman|Ça aide.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>horloge,verre_eau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1415,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le verre a glissé. Que fait Zoé ?</t>
+          <t>Le verre a glissé. Que fait Amir ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1500,7 +1571,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le verre a glissé. Que fait Zoé ?</t>
+          <t>narrateur|Le verre a glissé.
+narrateur|Que fait Amir ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1528,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Zoé a raconté. Papa et maman ont écouté.</t>
+          <t>Amir a raconté. Papa et maman ont écouté. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Amir. J'ai raconté. On a essuyé. Oui. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1672,7 +1744,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Zoé a raconté. Papa et maman ont écouté.</t>
+          <t>narrateur|Amir a raconté.
+narrateur|Papa et maman ont écouté.
+papa|Merci d'avoir raconté.
+maman|On raconte à papa ou maman.
+papa|Bravo, Amir.
+enfant-m|J'ai raconté.
+enfant-m|On a essuyé.
+maman|Oui.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1700,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa pose un nouveau verre. Zoé sourit.</t>
+          <t>Papa pose un nouveau verre. Il est au milieu de la table. Tu veux t'asseoir un peu ? Oui. Près du coussin bleu. Le rideau est calme, maintenant. L'horloge fait encore tic. La mouche n'est plus sur la vitre. L'eau n'est plus sur la table. Le nœud est parti. Tu veux regarder le coussin avec moi ? Oui. La petite boucle.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1920,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa pose un nouveau verre. Zoé sourit.</t>
+          <t>narrateur|Papa pose un nouveau verre.
+narrateur|Il est au milieu de la table.
+maman|Tu veux t'asseoir un peu ?
+enfant-m|Oui.
+enfant-m|Près du coussin bleu.
+papa|Le rideau est calme, maintenant.
+narrateur|L'horloge fait encore tic.
+narrateur|La mouche n'est plus sur la vitre.
+maman|L'eau n'est plus sur la table.
+enfant-m|Le nœud est parti.
+papa|Tu veux regarder le coussin avec moi ?
+enfant-m|Oui.
+enfant-m|La petite boucle.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raconté. Papa a écouté. Bravo. Tu as fait du bon travail. Le coussin bleu redevient doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2100,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai raconté.
+enfant-m|Papa a écouté.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le coussin bleu redevient doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'horloge du salon fait tic. Un rideau se lève un peu. Le vent entre, tout doux. Un coussin bleu a une petite boucle. La nappe est lisse sous la main. Un rayon de soleil touche la table. Le bois sent le chaud. Une mouche marche sur la vitre. Elle fait un petit point noir. Le coussin bleu est un peu rêche. Tu as entendu l'horloge, Amir ? Oui, papa. Elle fait tic. Le rideau danse un peu. Tu le vois ? Oui. Il va et vient. En ce moment, Amir touche le verre. Un verre d'eau a glissé. L'eau est sur la table. Elle fait une tache claire. Amir a un nœud au ventre. Papa est près de la fenêtre. Maman est dans la cuisine. Amir va vers papa. Il va raconter. Papa, le verre a glissé. L'eau est sur la table. Je t'écoute, Amir. Merci d'avoir su raconter. On le dit à papa ou maman. Tu as fait du bon travail. Tu veux le torchon ? Oui, papa. Maman arrive. Elle sent le savon de la cuisine. Maman, le verre a glissé. J'ai raconté à papa. Je t'écoute aussi. Merci Amir. On raconte à papa ou maman. Bravo. On essuie ensemble ? Oui. Amir aide à essuyer. Le torchon est épais et un peu rêche. La tache part. Le nœud se desserre. Tu veux un nouveau verre, plus loin ? Oui. Plus loin. On le pose au milieu, d'accord ? D'accord. Papa pose le verre, tout doucement. Il ne tremble plus. Le nœud au ventre, il est parti ? Oui, papa. Presque. Tu as su raconter. Ça aide.</t>
+          <t>L'horloge du salon fait tic. Un rideau se lève un peu. Le vent entre, tout doux. Un coussin bleu a une petite boucle. La nappe est lisse sous la main. Un rayon de soleil touche la table. Le bois sent le chaud. Une mouche marche sur la vitre. Elle fait un petit point noir. Le coussin bleu est un peu rêche. Tu as entendu l'horloge, Amir ? Oui, papa. Elle fait tic. Le rideau danse un peu. Tu le vois ? Oui. Il va et vient. En ce moment, Amir touche le verre. Un verre d'eau a glissé. L'eau est sur la table. Elle fait une tache claire. Amir a un nœud au ventre. Papa est près de la fenêtre. Maman est dans la cuisine. Amir va vers papa. Il va raconter. Papa, le verre a glissé. L'eau est sur la table. Je t'écoute, Amir. Merci d'avoir su raconter. On le dit à papa ou maman. Tu veux le torchon ? Oui, papa. Maman arrive. Elle sent le savon de la cuisine. Maman, le verre a glissé. J'ai raconté à papa. Je t'écoute aussi. Merci Amir. On raconte à papa ou maman. Bravo. On essuie ensemble ? Oui. Amir aide à essuyer. Le torchon est épais et un peu rêche. La tache part. Le nœud se desserre. Tu veux un nouveau verre, plus loin ? Oui. Plus loin. On le pose au milieu, d'accord ? D'accord. Papa pose le verre, tout doucement. Il ne tremble plus. Le nœud au ventre, il est parti ? Oui, papa. Presque. Tu as su raconter. Ça aide.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Zoé est dans le salon. Un verre d'eau a glissé. L'eau est sur la table. Zoé a un nœud au ventre. Papa est près de la fenêtre. Maman est dans la cuisine. Zoé va vers papa. Elle va &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. Elle dit : papa, le verre a glissé. Papa l'écoute. Maman arrive. Zoé raconte aussi à maman. Papa dit : merci d'avoir su raconter. On le dit à papa ou maman. Zoé aide à essuyer. Le nœud se desserre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'horloge du salon fait tic. Un rideau se lève un peu. Le vent entre, tout doux. Un coussin bleu a une petite boucle. La nappe est lisse sous la main. Un rayon de soleil touche la table. Le bois sent le chaud. Une mouche marche sur la vitre. Elle fait un petit point noir. Le coussin bleu est un peu rêche. Tu as entendu l'horloge, Amir ? Oui, papa. Elle fait tic. Le rideau danse un peu. Tu le vois ? Oui. Il va et vient. En ce moment, Amir touche le verre. Un verre d'eau a glissé. L'eau est sur la table. Elle fait une tache claire. Amir a un nœud au ventre. Papa est près de la fenêtre. Maman est dans la cuisine. Amir va vers papa. Il va raconter. Papa, le verre a glissé. L'eau est sur la table. Je t'écoute, Amir. Merci d'avoir su raconter. On le dit à papa ou maman. Tu veux le torchon ? Oui, papa. Maman arrive. Elle sent le savon de la cuisine. Maman, le verre a glissé. J'ai raconté à papa. Je t'écoute aussi. Merci Amir. On raconte à papa ou maman. Bravo. On essuie ensemble ? Oui. Amir aide à essuyer. Le torchon est épais et un peu rêche. La tache part. Le nœud se desserre. Tu veux un nouveau verre, plus loin ? Oui. Plus loin. On le pose au milieu, d'accord ? D'accord. Papa pose le verre, tout doucement. Il ne tremble plus. Le nœud au ventre, il est parti ? Oui, papa. Presque. Tu as su raconter. Ça aide.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1355,7 +1355,6 @@
 papa|Je t'écoute, Amir.
 papa|Merci d'avoir su raconter.
 papa|On le dit à papa ou maman.
-papa|Tu as fait du bon travail.
 papa|Tu veux le torchon ?
 enfant-m|Oui, papa.
 narrateur|Maman arrive.
@@ -1420,7 +1419,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le verre a glissé. Que fait Zoé ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le verre a glissé. Que fait Amir ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1575,7 +1574,6 @@
 narrateur|Que fait Amir ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1600,12 +1598,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a raconté. Papa et maman ont écouté. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Amir. J'ai raconté. On a essuyé. Oui. C'est du bon travail.</t>
+          <t>Amir a raconté. Papa et maman ont écouté. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Amir. J'ai raconté. On a essuyé. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Zoé a raconté. &lt;emphasis level="moderate"&gt;papa&lt;/emphasis&gt; et maman ont écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a raconté. Papa et maman ont écouté. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Amir. J'ai raconté. On a essuyé. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1751,11 +1749,9 @@
 papa|Bravo, Amir.
 enfant-m|J'ai raconté.
 enfant-m|On a essuyé.
-maman|Oui.
-maman|C'est du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+maman|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1785,7 +1781,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;&lt;emphasis level="moderate"&gt;papa&lt;/emphasis&gt; pose un nouveau verre. Zoé sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa pose un nouveau verre. Il est au milieu de la table. Tu veux t'asseoir un peu ? Oui. Près du coussin bleu. Le rideau est calme, maintenant. L'horloge fait encore tic. La mouche n'est plus sur la vitre. L'eau n'est plus sur la table. Le nœud est parti. Tu veux regarder le coussin avec moi ? Oui. La petite boucle.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1935,7 +1931,6 @@
 enfant-m|La petite boucle.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1960,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté. Papa a écouté. Bravo. Tu as fait du bon travail. Le coussin bleu redevient doux. L'histoire est finie.</t>
+          <t>J'ai raconté. Papa a écouté. Bravo. Le coussin bleu redevient doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai raconté. Papa a écouté. Bravo. Le coussin bleu redevient doux.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,12 +2098,9 @@
           <t>enfant-m|J'ai raconté.
 enfant-m|Papa a écouté.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le coussin bleu redevient doux.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le coussin bleu redevient doux.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-03.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zoé, papa, maman</t>
+          <t>Amir, papa, maman</t>
         </is>
       </c>
     </row>
